--- a/bm/MH/ISO.BM-MH-06-01 Phiếu yêu cầu mua hàng.xlsx
+++ b/bm/MH/ISO.BM-MH-06-01 Phiếu yêu cầu mua hàng.xlsx
@@ -63,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -85,11 +85,110 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,6 +214,16 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -495,47 +604,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>CÔNG TY QS TECHNOLOGY</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Mã số: ISO.BM-MH-06-01</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Ngày ban hành: 15/06/2026</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="F2" s="11" t="n"/>
+      <c r="G2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Lần ban hành: 01</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -547,36 +656,36 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Số phiếu:  ________________________________</t>
+          <t>Số phiếu:  ................................</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Ngày:  ________________________________</t>
+          <t>Ngày:  ................................</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bộ phận yêu cầu:  ________________________________</t>
+          <t>Bộ phận yêu cầu:  ................................</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Người yêu cầu:  ________________________________</t>
+          <t>Người yêu cầu:  ................................</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Mục đích sử dụng:  ________________________________</t>
+          <t>Mục đích sử dụng:  ................................</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Ngày cần hàng:  ________________________________</t>
+          <t>Ngày cần hàng:  ................................</t>
         </is>
       </c>
     </row>
@@ -740,28 +849,28 @@
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D18"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="D18"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="E7:H7"/>
     <mergeCell ref="A19"/>
     <mergeCell ref="C19"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="E2:G2"/>
     <mergeCell ref="C18"/>
     <mergeCell ref="D19"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E7:G7"/>
     <mergeCell ref="B18"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:D3"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="E3:G3"/>
     <mergeCell ref="A18"/>
+    <mergeCell ref="E5:G5"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="E6:H6"/>
     <mergeCell ref="B19"/>
+    <mergeCell ref="E1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9"/>
